--- a/MIP/Mexico/MIP_Mexico_2003.xlsx
+++ b/MIP/Mexico/MIP_Mexico_2003.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="g_produccion" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W_valor_agregado" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="f_demanda_final" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_importado" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ajuste_intermedio" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="multiplicadores" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balances_sectoriales" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="validacion_resumen" sheetId="13" state="visible" r:id="rId13"/>
@@ -34,7 +34,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'g_produccion'!$A$1:$B$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'W_valor_agregado'!$A$1:$B$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'f_demanda_final'!$A$1:$B$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'CI_importado'!$A$1:$B$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'ajuste_intermedio'!$A$1:$B$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'multiplicadores'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'balances_sectoriales'!$A$1:$M$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'validacion_resumen'!$A$1:$C$12</definedName>
@@ -640,12 +640,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>descripcion_CI_importado</t>
+          <t>descripcion_ajuste_intermedio</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Consumo intermedio importado fuera de Z; cierre VA: g = colsum(Z nacional) + CI importado + W.</t>
+          <t>Ajuste intermedio fuera de Z. En MIP directas puede ser CI importado; en COU reconstruidos con puente de precios puede incluir importaciones, margenes, impuestos y diferencias de valoracion comprador-basico.</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       <c r="A1" s="2" t="n"/>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>ci_importado</t>
+          <t>ajuste_intermedio_no_basico</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>consumo_intermedio_importado</t>
+          <t>ajuste_intermedio_no_basico</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>consumo_intermedio_importado</t>
+          <t>ajuste_intermedio_no_basico</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">

--- a/MIP/Mexico/MIP_Mexico_2003.xlsx
+++ b/MIP/Mexico/MIP_Mexico_2003.xlsx
@@ -47,13 +47,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -89,13 +92,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -115,13 +124,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -494,13 +506,13 @@
     <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="64" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
@@ -628,12 +640,12 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>HOJA</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>CONTENIDO</t>
         </is>
@@ -845,115 +857,115 @@
     <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="64" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>sector_vendedor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>11---Agricultura, ganadería, aprovechamiento forestal, pesca y caza</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>21---Minería</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>22---Electricidad, agua y suministro de gas por ductos al consumidor final</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>23---Construcción</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>31-33---Industrias manufactureras</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>43-46---Comercio</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>48---Transportes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>49---Correos y almacenamiento</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>51---Información en medios masivos</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>52---Servicios financieros y de seguros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>53---Servicios inmobiliarios y de alquiler de bienes muebles e intangibles</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>54---Servicios profesionales, científicos y técnicos</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>55---Dirección de corporativos y empresas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>56---Servicios de apoyo a los negocios y manejo de desechos y servicios de remediación</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>61---Servicios educativos</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>62---Servicios de salud y de asistencia social</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>71---Servicios de esparcimiento culturales y deportivos, y otros servicios recreativos</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>72---Servicios de alojamiento temporal y de preparación de alimentos y bebidas</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>81---Otros servicios excepto actividades del Gobierno</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>93---Actividades del Gobierno y de organismos internacionales y extraterritoriales</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>11---Agricultura, ganadería, aprovechamiento forestal, pesca y caza</t>
         </is>
@@ -1020,7 +1032,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>21---Minería</t>
         </is>
@@ -1087,7 +1099,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>22---Electricidad, agua y suministro de gas por ductos al consumidor final</t>
         </is>
@@ -1154,7 +1166,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>23---Construcción</t>
         </is>
@@ -1221,7 +1233,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>31-33---Industrias manufactureras</t>
         </is>
@@ -1288,7 +1300,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>43-46---Comercio</t>
         </is>
@@ -1355,7 +1367,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>48---Transportes</t>
         </is>
@@ -1422,7 +1434,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>49---Correos y almacenamiento</t>
         </is>
@@ -1489,7 +1501,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>51---Información en medios masivos</t>
         </is>
@@ -1556,7 +1568,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>52---Servicios financieros y de seguros</t>
         </is>
@@ -1623,7 +1635,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>53---Servicios inmobiliarios y de alquiler de bienes muebles e intangibles</t>
         </is>
@@ -1690,7 +1702,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>54---Servicios profesionales, científicos y técnicos</t>
         </is>
@@ -1757,7 +1769,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>55---Dirección de corporativos y empresas</t>
         </is>
@@ -1824,7 +1836,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>56---Servicios de apoyo a los negocios y manejo de desechos y servicios de remediación</t>
         </is>
@@ -1891,7 +1903,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>61---Servicios educativos</t>
         </is>
@@ -1958,7 +1970,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>62---Servicios de salud y de asistencia social</t>
         </is>
@@ -2025,7 +2037,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>71---Servicios de esparcimiento culturales y deportivos, y otros servicios recreativos</t>
         </is>
@@ -2092,7 +2104,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>72---Servicios de alojamiento temporal y de preparación de alimentos y bebidas</t>
         </is>
@@ -2159,7 +2171,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>81---Otros servicios excepto actividades del Gobierno</t>
         </is>
@@ -2226,7 +2238,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>93---Actividades del Gobierno y de organismos internacionales y extraterritoriales</t>
         </is>
@@ -2330,115 +2342,115 @@
     <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="64" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>sector_vendedor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>11---Agricultura, ganadería, aprovechamiento forestal, pesca y caza</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>21---Minería</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>22---Electricidad, agua y suministro de gas por ductos al consumidor final</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>23---Construcción</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>31-33---Industrias manufactureras</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>43-46---Comercio</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>48---Transportes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>49---Correos y almacenamiento</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>51---Información en medios masivos</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>52---Servicios financieros y de seguros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>53---Servicios inmobiliarios y de alquiler de bienes muebles e intangibles</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>54---Servicios profesionales, científicos y técnicos</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>55---Dirección de corporativos y empresas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>56---Servicios de apoyo a los negocios y manejo de desechos y servicios de remediación</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>61---Servicios educativos</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>62---Servicios de salud y de asistencia social</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>71---Servicios de esparcimiento culturales y deportivos, y otros servicios recreativos</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>72---Servicios de alojamiento temporal y de preparación de alimentos y bebidas</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>81---Otros servicios excepto actividades del Gobierno</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>93---Actividades del Gobierno y de organismos internacionales y extraterritoriales</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>11---Agricultura, ganadería, aprovechamiento forestal, pesca y caza</t>
         </is>
@@ -2505,7 +2517,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>21---Minería</t>
         </is>
@@ -2572,7 +2584,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>22---Electricidad, agua y suministro de gas por ductos al consumidor final</t>
         </is>
@@ -2639,7 +2651,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>23---Construcción</t>
         </is>
@@ -2706,7 +2718,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>31-33---Industrias manufactureras</t>
         </is>
@@ -2773,7 +2785,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>43-46---Comercio</t>
         </is>
@@ -2840,7 +2852,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>48---Transportes</t>
         </is>
@@ -2907,7 +2919,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>49---Correos y almacenamiento</t>
         </is>
@@ -2974,7 +2986,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>51---Información en medios masivos</t>
         </is>
@@ -3041,7 +3053,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>52---Servicios financieros y de seguros</t>
         </is>
@@ -3108,7 +3120,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>53---Servicios inmobiliarios y de alquiler de bienes muebles e intangibles</t>
         </is>
@@ -3175,7 +3187,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>54---Servicios profesionales, científicos y técnicos</t>
         </is>
@@ -3242,7 +3254,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>55---Dirección de corporativos y empresas</t>
         </is>
@@ -3309,7 +3321,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>56---Servicios de apoyo a los negocios y manejo de desechos y servicios de remediación</t>
         </is>
@@ -3376,7 +3388,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>61---Servicios educativos</t>
         </is>
@@ -3443,7 +3455,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>62---Servicios de salud y de asistencia social</t>
         </is>
@@ -3510,7 +3522,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>71---Servicios de esparcimiento culturales y deportivos, y otros servicios recreativos</t>
         </is>
@@ -3577,7 +3589,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>72---Servicios de alojamiento temporal y de preparación de alimentos y bebidas</t>
         </is>
@@ -3644,7 +3656,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>81---Otros servicios excepto actividades del Gobierno</t>
         </is>
@@ -3711,7 +3723,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>93---Actividades del Gobierno y de organismos internacionales y extraterritoriales</t>
         </is>
@@ -3815,115 +3827,115 @@
     <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="64" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>sector_vendedor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>11---Agricultura, ganadería, aprovechamiento forestal, pesca y caza</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>21---Minería</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>22---Electricidad, agua y suministro de gas por ductos al consumidor final</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>23---Construcción</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>31-33---Industrias manufactureras</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>43-46---Comercio</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>48---Transportes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>49---Correos y almacenamiento</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>51---Información en medios masivos</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>52---Servicios financieros y de seguros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>53---Servicios inmobiliarios y de alquiler de bienes muebles e intangibles</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>54---Servicios profesionales, científicos y técnicos</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>55---Dirección de corporativos y empresas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>56---Servicios de apoyo a los negocios y manejo de desechos y servicios de remediación</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>61---Servicios educativos</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>62---Servicios de salud y de asistencia social</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>71---Servicios de esparcimiento culturales y deportivos, y otros servicios recreativos</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>72---Servicios de alojamiento temporal y de preparación de alimentos y bebidas</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>81---Otros servicios excepto actividades del Gobierno</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>93---Actividades del Gobierno y de organismos internacionales y extraterritoriales</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>11---Agricultura, ganadería, aprovechamiento forestal, pesca y caza</t>
         </is>
@@ -3990,7 +4002,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>21---Minería</t>
         </is>
@@ -4057,7 +4069,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>22---Electricidad, agua y suministro de gas por ductos al consumidor final</t>
         </is>
@@ -4124,7 +4136,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>23---Construcción</t>
         </is>
@@ -4191,7 +4203,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>31-33---Industrias manufactureras</t>
         </is>
@@ -4258,7 +4270,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>43-46---Comercio</t>
         </is>
@@ -4325,7 +4337,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>48---Transportes</t>
         </is>
@@ -4392,7 +4404,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>49---Correos y almacenamiento</t>
         </is>
@@ -4459,7 +4471,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>51---Información en medios masivos</t>
         </is>
@@ -4526,7 +4538,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>52---Servicios financieros y de seguros</t>
         </is>
@@ -4593,7 +4605,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>53---Servicios inmobiliarios y de alquiler de bienes muebles e intangibles</t>
         </is>
@@ -4660,7 +4672,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>54---Servicios profesionales, científicos y técnicos</t>
         </is>
@@ -4727,7 +4739,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>55---Dirección de corporativos y empresas</t>
         </is>
@@ -4794,7 +4806,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>56---Servicios de apoyo a los negocios y manejo de desechos y servicios de remediación</t>
         </is>
@@ -4861,7 +4873,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>61---Servicios educativos</t>
         </is>
@@ -4928,7 +4940,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>62---Servicios de salud y de asistencia social</t>
         </is>
@@ -4995,7 +5007,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>71---Servicios de esparcimiento culturales y deportivos, y otros servicios recreativos</t>
         </is>
@@ -5062,7 +5074,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>72---Servicios de alojamiento temporal y de preparación de alimentos y bebidas</t>
         </is>
@@ -5129,7 +5141,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>81---Otros servicios excepto actividades del Gobierno</t>
         </is>
@@ -5196,7 +5208,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>93---Actividades del Gobierno y de organismos internacionales y extraterritoriales</t>
         </is>
@@ -5300,115 +5312,115 @@
     <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="64" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>sector_vendedor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>11---Agricultura, ganadería, aprovechamiento forestal, pesca y caza</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>21---Minería</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>22---Electricidad, agua y suministro de gas por ductos al consumidor final</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>23---Construcción</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>31-33---Industrias manufactureras</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>43-46---Comercio</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>48---Transportes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>49---Correos y almacenamiento</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>51---Información en medios masivos</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>52---Servicios financieros y de seguros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>53---Servicios inmobiliarios y de alquiler de bienes muebles e intangibles</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>54---Servicios profesionales, científicos y técnicos</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>55---Dirección de corporativos y empresas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>56---Servicios de apoyo a los negocios y manejo de desechos y servicios de remediación</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>61---Servicios educativos</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>62---Servicios de salud y de asistencia social</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>71---Servicios de esparcimiento culturales y deportivos, y otros servicios recreativos</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>72---Servicios de alojamiento temporal y de preparación de alimentos y bebidas</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>81---Otros servicios excepto actividades del Gobierno</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>93---Actividades del Gobierno y de organismos internacionales y extraterritoriales</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>11---Agricultura, ganadería, aprovechamiento forestal, pesca y caza</t>
         </is>
@@ -5475,7 +5487,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>21---Minería</t>
         </is>
@@ -5542,7 +5554,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>22---Electricidad, agua y suministro de gas por ductos al consumidor final</t>
         </is>
@@ -5609,7 +5621,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>23---Construcción</t>
         </is>
@@ -5676,7 +5688,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>31-33---Industrias manufactureras</t>
         </is>
@@ -5743,7 +5755,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>43-46---Comercio</t>
         </is>
@@ -5810,7 +5822,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>48---Transportes</t>
         </is>
@@ -5877,7 +5889,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>49---Correos y almacenamiento</t>
         </is>
@@ -5944,7 +5956,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>51---Información en medios masivos</t>
         </is>
@@ -6011,7 +6023,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>52---Servicios financieros y de seguros</t>
         </is>
@@ -6078,7 +6090,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>53---Servicios inmobiliarios y de alquiler de bienes muebles e intangibles</t>
         </is>
@@ -6145,7 +6157,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>54---Servicios profesionales, científicos y técnicos</t>
         </is>
@@ -6212,7 +6224,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>55---Dirección de corporativos y empresas</t>
         </is>
@@ -6279,7 +6291,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>56---Servicios de apoyo a los negocios y manejo de desechos y servicios de remediación</t>
         </is>
@@ -6346,7 +6358,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>61---Servicios educativos</t>
         </is>
@@ -6413,7 +6425,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>62---Servicios de salud y de asistencia social</t>
         </is>
@@ -6480,7 +6492,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>71---Servicios de esparcimiento culturales y deportivos, y otros servicios recreativos</t>
         </is>
@@ -6547,7 +6559,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>72---Servicios de alojamiento temporal y de preparación de alimentos y bebidas</t>
         </is>
@@ -6614,7 +6626,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>81---Otros servicios excepto actividades del Gobierno</t>
         </is>
@@ -6681,7 +6693,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>93---Actividades del Gobierno y de organismos internacionales y extraterritoriales</t>
         </is>
@@ -6785,115 +6797,115 @@
     <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="64" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>sector_vendedor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>11---Agricultura, ganadería, aprovechamiento forestal, pesca y caza</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>21---Minería</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>22---Electricidad, agua y suministro de gas por ductos al consumidor final</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>23---Construcción</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>31-33---Industrias manufactureras</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>43-46---Comercio</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>48---Transportes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>49---Correos y almacenamiento</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>51---Información en medios masivos</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>52---Servicios financieros y de seguros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>53---Servicios inmobiliarios y de alquiler de bienes muebles e intangibles</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>54---Servicios profesionales, científicos y técnicos</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>55---Dirección de corporativos y empresas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>56---Servicios de apoyo a los negocios y manejo de desechos y servicios de remediación</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>61---Servicios educativos</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>62---Servicios de salud y de asistencia social</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>71---Servicios de esparcimiento culturales y deportivos, y otros servicios recreativos</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>72---Servicios de alojamiento temporal y de preparación de alimentos y bebidas</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>81---Otros servicios excepto actividades del Gobierno</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>93---Actividades del Gobierno y de organismos internacionales y extraterritoriales</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>11---Agricultura, ganadería, aprovechamiento forestal, pesca y caza</t>
         </is>
@@ -6960,7 +6972,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>21---Minería</t>
         </is>
@@ -7027,7 +7039,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>22---Electricidad, agua y suministro de gas por ductos al consumidor final</t>
         </is>
@@ -7094,7 +7106,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>23---Construcción</t>
         </is>
@@ -7161,7 +7173,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>31-33---Industrias manufactureras</t>
         </is>
@@ -7228,7 +7240,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>43-46---Comercio</t>
         </is>
@@ -7295,7 +7307,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>48---Transportes</t>
         </is>
@@ -7362,7 +7374,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>49---Correos y almacenamiento</t>
         </is>
@@ -7429,7 +7441,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>51---Información en medios masivos</t>
         </is>
@@ -7496,7 +7508,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>52---Servicios financieros y de seguros</t>
         </is>
@@ -7563,7 +7575,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>53---Servicios inmobiliarios y de alquiler de bienes muebles e intangibles</t>
         </is>
@@ -7630,7 +7642,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>54---Servicios profesionales, científicos y técnicos</t>
         </is>
@@ -7697,7 +7709,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>55---Dirección de corporativos y empresas</t>
         </is>
@@ -7764,7 +7776,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>56---Servicios de apoyo a los negocios y manejo de desechos y servicios de remediación</t>
         </is>
@@ -7831,7 +7843,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>61---Servicios educativos</t>
         </is>
@@ -7898,7 +7910,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>62---Servicios de salud y de asistencia social</t>
         </is>
@@ -7965,7 +7977,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>71---Servicios de esparcimiento culturales y deportivos, y otros servicios recreativos</t>
         </is>
@@ -8032,7 +8044,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>72---Servicios de alojamiento temporal y de preparación de alimentos y bebidas</t>
         </is>
@@ -8099,7 +8111,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>81---Otros servicios excepto actividades del Gobierno</t>
         </is>
@@ -8166,7 +8178,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>93---Actividades del Gobierno y de organismos internacionales y extraterritoriales</t>
         </is>
@@ -8257,50 +8269,50 @@
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="64" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>encadenamiento_atras_BL_Leontief_colsum_L</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>indice_atras_BL_Leontief</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>encadenamiento_adelante_FL_Leontief_rowsum_L</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>indice_adelante_FL_Leontief</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>encadenamiento_adelante_Ghosh_rowsum_G</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>indice_adelante_Ghosh</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>encadenamiento_atras_Ghosh_colsum_G</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>11---Agricultura, ganadería, aprovechamiento forestal, pesca y caza</t>
         </is>
@@ -8318,17 +8330,17 @@
         <v>0.9132868627954276</v>
       </c>
       <c r="F2" t="n">
-        <v>2.386975337764864</v>
+        <v>2.386975337764865</v>
       </c>
       <c r="G2" t="n">
-        <v>1.348175980808058</v>
+        <v>1.348175980808059</v>
       </c>
       <c r="H2" t="n">
         <v>1.432455146140563</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>21---Minería</t>
         </is>
@@ -8349,14 +8361,14 @@
         <v>2.214112572704816</v>
       </c>
       <c r="G3" t="n">
-        <v>1.250542199619414</v>
+        <v>1.250542199619415</v>
       </c>
       <c r="H3" t="n">
         <v>1.434117509422196</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>22---Electricidad, agua y suministro de gas por ductos al consumidor final</t>
         </is>
@@ -8374,7 +8386,7 @@
         <v>0.9279671846466643</v>
       </c>
       <c r="F4" t="n">
-        <v>2.220338743873351</v>
+        <v>2.220338743873352</v>
       </c>
       <c r="G4" t="n">
         <v>1.254058773204829</v>
@@ -8384,7 +8396,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>23---Construcción</t>
         </is>
@@ -8412,7 +8424,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>31-33---Industrias manufactureras</t>
         </is>
@@ -8436,11 +8448,11 @@
         <v>1.239169909034673</v>
       </c>
       <c r="H6" t="n">
-        <v>7.912501319892832</v>
+        <v>7.912501319892833</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>43-46---Comercio</t>
         </is>
@@ -8461,14 +8473,14 @@
         <v>1.702771644437597</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9617342062618098</v>
+        <v>0.9617342062618099</v>
       </c>
       <c r="H7" t="n">
         <v>2.336588480779102</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>48---Transportes</t>
         </is>
@@ -8496,7 +8508,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>49---Correos y almacenamiento</t>
         </is>
@@ -8524,7 +8536,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>51---Información en medios masivos</t>
         </is>
@@ -8548,11 +8560,11 @@
         <v>1.021692006523186</v>
       </c>
       <c r="H10" t="n">
-        <v>1.859110201659397</v>
+        <v>1.859110201659396</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>52---Servicios financieros y de seguros</t>
         </is>
@@ -8570,7 +8582,7 @@
         <v>1.028706472884306</v>
       </c>
       <c r="F11" t="n">
-        <v>2.184389978744315</v>
+        <v>2.184389978744314</v>
       </c>
       <c r="G11" t="n">
         <v>1.233754725266043</v>
@@ -8580,7 +8592,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>53---Servicios inmobiliarios y de alquiler de bienes muebles e intangibles</t>
         </is>
@@ -8601,14 +8613,14 @@
         <v>1.429237013660727</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8072404361343434</v>
+        <v>0.8072404361343435</v>
       </c>
       <c r="H12" t="n">
         <v>1.298056144349089</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>54---Servicios profesionales, científicos y técnicos</t>
         </is>
@@ -8632,11 +8644,11 @@
         <v>1.314163155763589</v>
       </c>
       <c r="H13" t="n">
-        <v>1.344344723004608</v>
+        <v>1.344344723004607</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>55---Dirección de corporativos y empresas</t>
         </is>
@@ -8657,14 +8669,14 @@
         <v>3.026693990846445</v>
       </c>
       <c r="G14" t="n">
-        <v>1.709492375206611</v>
+        <v>1.709492375206612</v>
       </c>
       <c r="H14" t="n">
         <v>1.094573109450205</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>56---Servicios de apoyo a los negocios y manejo de desechos y servicios de remediación</t>
         </is>
@@ -8692,7 +8704,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>61---Servicios educativos</t>
         </is>
@@ -8713,14 +8725,14 @@
         <v>1.01840237309295</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5751989123974315</v>
+        <v>0.5751989123974316</v>
       </c>
       <c r="H16" t="n">
         <v>1.172826814646606</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>62---Servicios de salud y de asistencia social</t>
         </is>
@@ -8748,7 +8760,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>71---Servicios de esparcimiento culturales y deportivos, y otros servicios recreativos</t>
         </is>
@@ -8776,7 +8788,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>72---Servicios de alojamiento temporal y de preparación de alimentos y bebidas</t>
         </is>
@@ -8804,7 +8816,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>81---Otros servicios excepto actividades del Gobierno</t>
         </is>
@@ -8832,7 +8844,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>93---Actividades del Gobierno y de organismos internacionales y extraterritoriales</t>
         </is>
@@ -8878,25 +8890,25 @@
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="64" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>bloque</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>fuente_resumen</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Tabla fuente original o referencia</t>
         </is>
@@ -9049,12 +9061,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>fuente_notas</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Tabla fuente original o referencia</t>
         </is>
@@ -9101,16 +9113,16 @@
     <col width="14" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="64" customHeight="1">
+      <c r="A1" s="2" t="n"/>
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>nota</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -9138,16 +9150,16 @@
     <col width="14" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="64" customHeight="1">
+      <c r="A1" s="2" t="n"/>
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>nota</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -9175,16 +9187,16 @@
     <col width="14" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="64" customHeight="1">
+      <c r="A1" s="2" t="n"/>
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>nota</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -9212,16 +9224,16 @@
     <col width="14" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1" ht="64" customHeight="1">
+      <c r="A1" s="2" t="n"/>
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>nota</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -9268,115 +9280,115 @@
     <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="64" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>sector_vendedor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>11---Agricultura, ganadería, aprovechamiento forestal, pesca y caza</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>21---Minería</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>22---Electricidad, agua y suministro de gas por ductos al consumidor final</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>23---Construcción</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>31-33---Industrias manufactureras</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>43-46---Comercio</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>48---Transportes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>49---Correos y almacenamiento</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>51---Información en medios masivos</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>52---Servicios financieros y de seguros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>53---Servicios inmobiliarios y de alquiler de bienes muebles e intangibles</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>54---Servicios profesionales, científicos y técnicos</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>55---Dirección de corporativos y empresas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>56---Servicios de apoyo a los negocios y manejo de desechos y servicios de remediación</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>61---Servicios educativos</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>62---Servicios de salud y de asistencia social</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>71---Servicios de esparcimiento culturales y deportivos, y otros servicios recreativos</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>72---Servicios de alojamiento temporal y de preparación de alimentos y bebidas</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>81---Otros servicios excepto actividades del Gobierno</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>93---Actividades del Gobierno y de organismos internacionales y extraterritoriales</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>11---Agricultura, ganadería, aprovechamiento forestal, pesca y caza</t>
         </is>
@@ -9443,7 +9455,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>21---Minería</t>
         </is>
@@ -9510,7 +9522,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>22---Electricidad, agua y suministro de gas por ductos al consumidor final</t>
         </is>
@@ -9577,7 +9589,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>23---Construcción</t>
         </is>
@@ -9644,7 +9656,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>31-33---Industrias manufactureras</t>
         </is>
@@ -9711,7 +9723,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>43-46---Comercio</t>
         </is>
@@ -9778,7 +9790,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>48---Transportes</t>
         </is>
@@ -9845,7 +9857,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>49---Correos y almacenamiento</t>
         </is>
@@ -9912,7 +9924,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>51---Información en medios masivos</t>
         </is>
@@ -9979,7 +9991,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>52---Servicios financieros y de seguros</t>
         </is>
@@ -10046,7 +10058,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>53---Servicios inmobiliarios y de alquiler de bienes muebles e intangibles</t>
         </is>
@@ -10113,7 +10125,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>54---Servicios profesionales, científicos y técnicos</t>
         </is>
@@ -10180,7 +10192,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>55---Dirección de corporativos y empresas</t>
         </is>
@@ -10247,7 +10259,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>56---Servicios de apoyo a los negocios y manejo de desechos y servicios de remediación</t>
         </is>
@@ -10314,7 +10326,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>61---Servicios educativos</t>
         </is>
@@ -10381,7 +10393,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>62---Servicios de salud y de asistencia social</t>
         </is>
@@ -10448,7 +10460,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>71---Servicios de esparcimiento culturales y deportivos, y otros servicios recreativos</t>
         </is>
@@ -10515,7 +10527,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>72---Servicios de alojamiento temporal y de preparación de alimentos y bebidas</t>
         </is>
@@ -10582,7 +10594,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>81---Otros servicios excepto actividades del Gobierno</t>
         </is>
@@ -10649,7 +10661,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>93---Actividades del Gobierno y de organismos internacionales y extraterritoriales</t>
         </is>
@@ -10739,45 +10751,45 @@
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="64" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>x_produccion_bruta</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>ventas_intermedias_Z</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>y_demanda_final_total</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>compras_intermedias_Z</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>ajuste_intermedio_no_basico</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>v_valor_agregado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>11---Agricultura, ganadería, aprovechamiento forestal, pesca y caza</t>
         </is>
@@ -10802,7 +10814,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>21---Minería</t>
         </is>
@@ -10827,7 +10839,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>22---Electricidad, agua y suministro de gas por ductos al consumidor final</t>
         </is>
@@ -10852,7 +10864,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>23---Construcción</t>
         </is>
@@ -10877,7 +10889,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>31-33---Industrias manufactureras</t>
         </is>
@@ -10902,7 +10914,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>43-46---Comercio</t>
         </is>
@@ -10927,7 +10939,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>48---Transportes</t>
         </is>
@@ -10952,7 +10964,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>49---Correos y almacenamiento</t>
         </is>
@@ -10977,7 +10989,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>51---Información en medios masivos</t>
         </is>
@@ -11002,7 +11014,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>52---Servicios financieros y de seguros</t>
         </is>
@@ -11027,7 +11039,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>53---Servicios inmobiliarios y de alquiler de bienes muebles e intangibles</t>
         </is>
@@ -11052,7 +11064,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>54---Servicios profesionales, científicos y técnicos</t>
         </is>
@@ -11077,7 +11089,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>55---Dirección de corporativos y empresas</t>
         </is>
@@ -11102,7 +11114,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>56---Servicios de apoyo a los negocios y manejo de desechos y servicios de remediación</t>
         </is>
@@ -11127,7 +11139,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>61---Servicios educativos</t>
         </is>
@@ -11152,7 +11164,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>62---Servicios de salud y de asistencia social</t>
         </is>
@@ -11177,7 +11189,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>71---Servicios de esparcimiento culturales y deportivos, y otros servicios recreativos</t>
         </is>
@@ -11202,7 +11214,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>72---Servicios de alojamiento temporal y de preparación de alimentos y bebidas</t>
         </is>
@@ -11227,7 +11239,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>81---Otros servicios excepto actividades del Gobierno</t>
         </is>
@@ -11252,7 +11264,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>93---Actividades del Gobierno y de organismos internacionales y extraterritoriales</t>
         </is>
@@ -11304,65 +11316,65 @@
     <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="64" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>C_consumo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>I_inversion</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>G_gasto_publico</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>X_exportaciones</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>sin_desglose_fuente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>M_importaciones</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>XN_exportaciones_netas</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>DA_C_I_G_XN</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>y_demanda_final_total_mip</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>diferencia_y_mip_menos_DA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>11---Agricultura, ganadería, aprovechamiento forestal, pesca y caza</t>
         </is>
@@ -11399,7 +11411,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>21---Minería</t>
         </is>
@@ -11436,7 +11448,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>22---Electricidad, agua y suministro de gas por ductos al consumidor final</t>
         </is>
@@ -11473,7 +11485,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>23---Construcción</t>
         </is>
@@ -11510,7 +11522,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>31-33---Industrias manufactureras</t>
         </is>
@@ -11547,7 +11559,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>43-46---Comercio</t>
         </is>
@@ -11584,7 +11596,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>48---Transportes</t>
         </is>
@@ -11621,7 +11633,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>49---Correos y almacenamiento</t>
         </is>
@@ -11658,7 +11670,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>51---Información en medios masivos</t>
         </is>
@@ -11695,7 +11707,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>52---Servicios financieros y de seguros</t>
         </is>
@@ -11732,7 +11744,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>53---Servicios inmobiliarios y de alquiler de bienes muebles e intangibles</t>
         </is>
@@ -11769,7 +11781,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>54---Servicios profesionales, científicos y técnicos</t>
         </is>
@@ -11806,7 +11818,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>55---Dirección de corporativos y empresas</t>
         </is>
@@ -11843,7 +11855,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>56---Servicios de apoyo a los negocios y manejo de desechos y servicios de remediación</t>
         </is>
@@ -11880,7 +11892,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>61---Servicios educativos</t>
         </is>
@@ -11917,7 +11929,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>62---Servicios de salud y de asistencia social</t>
         </is>
@@ -11954,7 +11966,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>71---Servicios de esparcimiento culturales y deportivos, y otros servicios recreativos</t>
         </is>
@@ -11991,7 +12003,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>72---Servicios de alojamiento temporal y de preparación de alimentos y bebidas</t>
         </is>
@@ -12028,7 +12040,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>81---Otros servicios excepto actividades del Gobierno</t>
         </is>
@@ -12065,7 +12077,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>93---Actividades del Gobierno y de organismos internacionales y extraterritoriales</t>
         </is>

--- a/MIP/Mexico/MIP_Mexico_2003.xlsx
+++ b/MIP/Mexico/MIP_Mexico_2003.xlsx
@@ -32,7 +32,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'D_market_share'!$A$1:$B$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Z_consumos_intermedios'!$A$1:$U$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'x_produccion_bruta'!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'y_demanda_final'!$A$1:$K$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'y_demanda_final'!$A$1:$M$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'X_hat'!$A$1:$U$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'A_coef_tecnicos'!$A$1:$U$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'L_leontief'!$A$1:$U$21</definedName>
@@ -743,7 +743,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Demanda final homologada: C, I, G, X, M, XN y DA = C + I + G + XN.</t>
+          <t>Demanda final por componente, tomada de las columnas del COU/fuente (C hogares, G gobierno, FBKF capital fijo, VE variacion de existencias, X, M) y repartida a las industrias con la participacion de mercado D. La VE puede ser negativa (desacumulacion de inventarios); por eso se separa de la FBKF (siempre &gt;= 0). El total reconcilia con el COU; ver glosario.</t>
         </is>
       </c>
     </row>
@@ -11300,7 +11300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -11314,6 +11314,8 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="64" customHeight="1">
@@ -11324,50 +11326,60 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>C_consumo</t>
+          <t>C_consumo_hogares</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>I_inversion</t>
+          <t>G_consumo_gobierno</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>G_gasto_publico</t>
+          <t>FBKF_capital_fijo</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>VE_variacion_existencias</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>X_exportaciones</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>sin_desglose_fuente</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>M_importaciones</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>inversion_FBKF_mas_VE</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>XN_exportaciones_netas</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>DA_C_I_G_XN</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>DA_demanda_agregada</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>y_demanda_final_total_mip</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>diferencia_y_mip_menos_DA</t>
         </is>
@@ -11392,11 +11404,11 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>158905279</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
@@ -11404,9 +11416,15 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>158905279</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>158905279</v>
       </c>
     </row>
@@ -11429,11 +11447,11 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>235540129</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
@@ -11441,9 +11459,15 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>235540129</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>235540129</v>
       </c>
     </row>
@@ -11466,11 +11490,11 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>85163278</v>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
@@ -11478,9 +11502,15 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>85163278</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>85163278</v>
       </c>
     </row>
@@ -11503,11 +11533,11 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>887257188</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
@@ -11515,9 +11545,15 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>887257188</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>887257188</v>
       </c>
     </row>
@@ -11540,11 +11576,11 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>1605345533</v>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
@@ -11552,9 +11588,15 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1605345533</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>1605345533</v>
       </c>
     </row>
@@ -11577,11 +11619,11 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>929600787</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
@@ -11589,9 +11631,15 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>929600787</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>929600787</v>
       </c>
     </row>
@@ -11614,11 +11662,11 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>596959367</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
@@ -11626,9 +11674,15 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>596959367</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>596959367</v>
       </c>
     </row>
@@ -11651,11 +11705,11 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>8584217</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
@@ -11663,9 +11717,15 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>8584217</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>8584217</v>
       </c>
     </row>
@@ -11688,11 +11748,11 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>169717880</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
@@ -11700,9 +11760,15 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>169717880</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>169717880</v>
       </c>
     </row>
@@ -11725,11 +11791,11 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>111983348</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
@@ -11737,9 +11803,15 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>111983348</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>111983348</v>
       </c>
     </row>
@@ -11762,11 +11834,11 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>673168314</v>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
@@ -11774,9 +11846,15 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>673168314</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>673168314</v>
       </c>
     </row>
@@ -11799,11 +11877,11 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>110189483</v>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
@@ -11811,9 +11889,15 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>110189483</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>110189483</v>
       </c>
     </row>
@@ -11853,6 +11937,12 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -11873,11 +11963,11 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>23965976</v>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
@@ -11885,9 +11975,15 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>23965976</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>23965976</v>
       </c>
     </row>
@@ -11910,11 +12006,11 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
         <v>410347890</v>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
@@ -11922,9 +12018,15 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>410347890</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>410347890</v>
       </c>
     </row>
@@ -11947,11 +12049,11 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>293306066</v>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
@@ -11959,9 +12061,15 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>293306066</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>293306066</v>
       </c>
     </row>
@@ -11984,11 +12092,11 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>39487725</v>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -11996,9 +12104,15 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>39487725</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>39487725</v>
       </c>
     </row>
@@ -12021,11 +12135,11 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
         <v>244482929</v>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
@@ -12033,9 +12147,15 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>244482929</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>244482929</v>
       </c>
     </row>
@@ -12058,11 +12178,11 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>204364802</v>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
@@ -12070,9 +12190,15 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>204364802</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>204364802</v>
       </c>
     </row>
@@ -12095,11 +12221,11 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
         <v>416928743</v>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
@@ -12107,14 +12233,20 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>416928743</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>416928743</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K21"/>
+  <autoFilter ref="A1:M21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>